--- a/sharedata/excel/Z-专属装备表(ExclusiveEquipmentData).xlsx
+++ b/sharedata/excel/Z-专属装备表(ExclusiveEquipmentData).xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255" tabRatio="985"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>等级解锁</t>
   </si>
@@ -120,6 +125,27 @@
   </si>
   <si>
     <t>ref(SkillData)</t>
+  </si>
+  <si>
+    <t>临时英雄_1_专属装备</t>
+  </si>
+  <si>
+    <t>临时英雄_1</t>
+  </si>
+  <si>
+    <t>4星</t>
+  </si>
+  <si>
+    <t>5星</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>临时专属技能_lv1</t>
   </si>
 </sst>
 </file>
@@ -152,6 +178,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -301,13 +334,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -636,153 +662,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -801,11 +827,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1279,13 +1302,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="22" style="3" customWidth="1"/>
+    <col min="1" max="1" width="17.3333333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="6.44444444444444" style="3" customWidth="1"/>
-    <col min="3" max="3" width="6.66666666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.8888888888889" style="3" customWidth="1"/>
     <col min="4" max="4" width="11.7777777777778" style="3" customWidth="1"/>
-    <col min="5" max="9" width="15.3333333333333" style="3" customWidth="1"/>
+    <col min="5" max="6" width="15.3333333333333" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.3333333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14.8888888888889" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1418,30 +1444,30 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="66.0" customHeight="1">
-      <c r="B7" t="n" s="6">
+    <row r="7" spans="1:9">
+      <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" t="str" s="7">
-        <v>临时英雄_1_专属装备</v>
-      </c>
-      <c r="D7" t="str" s="7">
-        <v>临时英雄_1</v>
-      </c>
-      <c r="E7" t="str" s="6">
-        <v>4星</v>
-      </c>
-      <c r="F7" t="str" s="6">
-        <v>5星</v>
-      </c>
-      <c r="G7" t="str" s="6">
-        <v>紫</v>
-      </c>
-      <c r="H7" t="str" s="6">
-        <v>1</v>
-      </c>
-      <c r="I7" t="str" s="7">
-        <v>临时专属技能_lv1</v>
+      <c r="C7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
